--- a/PTBR/Lang/PTBR/Dialog/Drama/namamani.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/namamani.xlsx
@@ -428,7 +428,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O que é este lugar?</t>
+          <t>Que lugar é este?</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sobre criações imperfeitas.</t>
+          <t>Sobre miscriações.</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Você está carregando uma máquina curiosa. Deixe-me dar uma olhada.</t>
+          <t>Está carregando uma máquina curiosa. Deixa eu ver.</t>
         </is>
       </c>
     </row>
@@ -547,9 +547,9 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>... Exatamente como eu pensei. A fiação está desleixada. Atrasos de sinal, flutuações de corrente, sincronização das engrenagens do relógio - tudo no limite. Você nem está usando metade do potencial desta máquina de computação.
-O layout dos condutores está uma bagunça, e mal tem gravações anti-interferência. Se você reposicionar a linha de aterramento, isso deve eliminar a maior parte do ruído... Hã, os símbolos de controle também precisam de otimização. Deixe as engrenagens de memória dinâmicas, e a eficiência de processamento vai disparar.
-... Interessante. Não posso dizer que eu não gosto desse tipo de artesanato bruto. Você tem um chip de memória aí?</t>
+          <t>...Como imaginava. O circuito é torto. Atrasos de sinal, flutuações de corrente, sincronização das engrenagens do relógio: tudo empurrado ao limite. Você não está nem usando metade do potencial deste motor de computação.
+O traçado dos condutores é uma bagunça, e quase não há gravação anti-interferência. Se redirecionar o fio-terra, isso corta a maior parte do ruído...Hã, os selos de controle podiam ser otimizados também. Torne as engrenagens de memória dinâmicas e a eficiência de processamento vai voar.
+...Interessante. Não posso dizer que desgosto desse artesanato grosseiro. Tem um chip de memória com você?</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Talvez mais tarde.</t>
+          <t>Talvez depois.</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Uma criação imperfeita? Isso é apenas uma desculpa de um engenheiro incompetente.</t>
+          <t>Uma miscriação? Isso é desculpa de engenheiro incompetente.</t>
         </is>
       </c>
     </row>
@@ -725,8 +725,8 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>...Certo, isso deve funcionar.
-Está ouvindo? As engrenagens cantando umas para as outras—o coração pulsante de uma máquina perfeita.</t>
+          <t>...Certo, isso deve resolver.
+Ouviu? As engrenagens cantando entre si: o coração de uma máquina perfeita.</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Aqui, pegue este componente velho que eu tirei dela. Considere como uma lembrança.</t>
+          <t>Toma, leve este componente velho que tirei dele. Considere uma lembrança.</t>
         </is>
       </c>
     </row>
